--- a/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
+++ b/assets/docs/lop1/Hoat dong trai nghiem - Lop 1.xlsx
@@ -1393,7 +1393,7 @@
       <c r="H29" s="4" t="inlineStr">
         <is>
           <t>Năng lực số 2.5 CB1a: HS xem phim tình huống và chọn được cách ứng xử phù hợp với bạn bè, thầy cô.
-QPAN: Tổ chức hoạt động tìm hiểu, thăm hỏi, tri ân gia đình thương binh, liệt sĩ, đơn vị bộ đội, công an trên địa bàn; giới thiệu hình ảnh chú bộ đội Quân đội nhân dân, chú công an Công an nhân dân và di tích lịch sử ở địa phương.</t>
+Học tập và làm theo Bác: Điều 3 “Đoàn kết tốt, kỉ luật tốt” (mạch 3): HS nói một việc thân thiện đã làm cho bạn hôm nay (chào bạn, cho bạn mượn bút, rủ bạn chơi cùng); GV chốt: đó là làm theo lời Bác dạy “đoàn kết tốt”.</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,8 @@
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
+          <t>Học tập và làm theo Bác: Năm điều Bác Hồ dạy (mạch 1–5): HS cả trường đọc đồng thanh Năm điều; mỗi lớp chọn một điều làm nội dung thi đua của lớp trong tháng và nói một việc cụ thể sẽ làm.
+KNS: KN tự đánh giá và đánh giá bạn một cách khách quan, thiện chí.</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1496,8 @@
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>Năng lực số 2.5 CB1a: HS xem phim tình huống và chọn được cách ứng xử phù hợp với bạn bè, thầy cô.</t>
+          <t>Năng lực số 2.5 CB1a: HS xem phim tình huống và chọn được cách ứng xử phù hợp với bạn bè, thầy cô.
+Học tập và làm theo Bác: Năm điều Bác Hồ dạy (mạch 1–5): mỗi HS nhận một việc nhỏ theo một điều (VD điều 4: rửa tay trước khi ăn, giữ bàn học sạch), làm trong tuần và kể lại ở giờ sinh hoạt Sao cuối tuần.</t>
         </is>
       </c>
     </row>
@@ -3334,7 +3336,7 @@
       <c r="D88" s="4" t="inlineStr"/>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Sinh hoạt dướ cờ: Chăm sóc vườn cây nhà trường</t>
+          <t>Sinh hoạt dưới cờ: Chăm sóc vườn cây nhà trường</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
